--- a/skills/xlsx/templates/atlas_default.xlsx
+++ b/skills/xlsx/templates/atlas_default.xlsx
@@ -44,7 +44,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D97757"/>
+        <fgColor rgb="00371447"/>
       </patternFill>
     </fill>
   </fills>
